--- a/survey_templates/031_medical_task_disclosure_survey--survey_templates.xlsx
+++ b/survey_templates/031_medical_task_disclosure_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -768,23 +768,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>task_clarity_2</t>
+          <t>clinical_responsibilities_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Task Clarity</t>
+          <t>Clinical Responsibilities 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>clinical_responsibilities_2</t>
+          <t>training_needs_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Clinical Responsibilities</t>
+          <t>Training Needs 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,40 +814,40 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>training_needs_2</t>
+          <t>work_hours_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Training Needs</t>
+          <t>Work Hours 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>clinical_tasks_2</t>
+          <t>staff_feedback_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Clinical Tasks</t>
+          <t>Staff Feedback 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>work_hours_2</t>
+          <t>task_clarity_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Work Hours</t>
+          <t>Task Clarity 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,205 +883,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>staff_feedback_2</t>
+          <t>clinical_tasks_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Staff Feedback</t>
+          <t>Clinical Tasks 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>email_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>phone_2</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>name_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>date_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>time_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>task_clarity_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Task Clarity</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>clinical_responsibilities_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Clinical Responsibilities</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>clinical_tasks_2</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Clinical Tasks</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1279,255 +1095,153 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>task_clarity_2_choices</t>
+          <t>clinical_responsibilities_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>clear</t>
+          <t>task_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Task 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>task_clarity_2_choices</t>
+          <t>clinical_responsibilities_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>task_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Unclear</t>
+          <t>Task 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>task_clarity_2_choices</t>
+          <t>clinical_responsibilities_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>task_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Not Applicable</t>
+          <t>Task 3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>clinical_responsibilities_2_choices</t>
+          <t>training_needs_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>task_1</t>
+          <t>training_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Task 1</t>
+          <t>Training 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>clinical_responsibilities_2_choices</t>
+          <t>training_needs_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>task_2</t>
+          <t>training_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Task 2</t>
+          <t>Training 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>clinical_responsibilities_2_choices</t>
+          <t>training_needs_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>task_3</t>
+          <t>training_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Task 3</t>
+          <t>Training 3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>training_needs_2_choices</t>
+          <t>task_clarity_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>training_1</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Training 1</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>training_needs_2_choices</t>
+          <t>task_clarity_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>training_2</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Training 2</t>
+          <t>Unclear</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>training_needs_2_choices</t>
+          <t>task_clarity_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>training_3</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Training 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>task_clarity_3_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>clear</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>task_clarity_3_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>unclear</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>task_clarity_3_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
           <t>Not Applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>clinical_responsibilities_3_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>task_1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Task 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>clinical_responsibilities_3_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>task_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Task 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>clinical_responsibilities_3_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>task_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Task 3</t>
         </is>
       </c>
     </row>
